--- a/project/outputs_xlsx_solution/test2.4-wide-NC-1.xlsx
+++ b/project/outputs_xlsx_solution/test2.4-wide-NC-1.xlsx
@@ -728,12 +728,9 @@
         <v>8</v>
       </c>
       <c r="M9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N9" t="s">
-        <v>9</v>
-      </c>
-      <c r="O9" t="s">
         <v>11</v>
       </c>
       <c r="P9" t="s">
@@ -759,10 +756,10 @@
       <c r="M10" t="s">
         <v>10</v>
       </c>
+      <c r="N10" t="s">
+        <v>9</v>
+      </c>
       <c r="O10" t="s">
-        <v>9</v>
-      </c>
-      <c r="P10" t="s">
         <v>11</v>
       </c>
       <c r="Q10" t="s">
@@ -786,12 +783,9 @@
         <v>8</v>
       </c>
       <c r="N11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O11" t="s">
-        <v>9</v>
-      </c>
-      <c r="P11" t="s">
         <v>11</v>
       </c>
       <c r="R11" t="s">
@@ -817,10 +811,10 @@
       <c r="N12" t="s">
         <v>10</v>
       </c>
+      <c r="O12" t="s">
+        <v>9</v>
+      </c>
       <c r="P12" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" t="s">
         <v>11</v>
       </c>
       <c r="S12" t="s">
